--- a/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana</t>
+          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,05; 43,75</t>
+          <t>40,0; 43,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,7; 40,97</t>
+          <t>35,97; 40,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,42; 39,68</t>
+          <t>35,67; 39,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,36; 42,29</t>
+          <t>37,11; 41,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,67; 42,06</t>
+          <t>38,7; 41,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 40,37</t>
+          <t>35,66; 40,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,35; 40,23</t>
+          <t>35,68; 40,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,62; 38,56</t>
+          <t>34,42; 38,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,81; 42,27</t>
+          <t>39,73; 42,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,49; 40,03</t>
+          <t>36,54; 40,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 39,42</t>
+          <t>36,09; 39,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 39,47</t>
+          <t>36,49; 39,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,76; 40,61</t>
+          <t>37,72; 40,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 38,62</t>
+          <t>35,45; 38,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 39,5</t>
+          <t>35,44; 39,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,07; 38,39</t>
+          <t>36,05; 38,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,97; 39,88</t>
+          <t>36,96; 39,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 40,09</t>
+          <t>35,82; 39,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,6</t>
+          <t>36,21; 39,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,49; 40,4</t>
+          <t>37,54; 40,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,87; 39,81</t>
+          <t>37,84; 39,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 38,85</t>
+          <t>36,25; 38,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,26; 38,85</t>
+          <t>36,3; 38,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,36; 39,26</t>
+          <t>37,28; 39,26</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,17; 40,67</t>
+          <t>37,4; 40,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,68; 38,72</t>
+          <t>34,83; 38,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,56; 38,83</t>
+          <t>34,73; 38,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,09; 39,11</t>
+          <t>36,15; 38,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,44; 39,76</t>
+          <t>36,37; 39,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,08; 39,44</t>
+          <t>35,45; 39,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,16; 39,54</t>
+          <t>35,33; 39,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 39,25</t>
+          <t>35,63; 39,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 39,59</t>
+          <t>37,33; 39,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,71; 38,59</t>
+          <t>35,7; 38,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,54; 38,51</t>
+          <t>35,6; 38,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,3; 38,64</t>
+          <t>36,21; 38,48</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,05; 40,25</t>
+          <t>37,12; 40,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,4; 39,09</t>
+          <t>36,22; 39,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,82; 38,16</t>
+          <t>34,97; 38,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 37,79</t>
+          <t>34,52; 37,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,67; 40,42</t>
+          <t>37,83; 40,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,16; 39,57</t>
+          <t>36,4; 39,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,84; 38,84</t>
+          <t>35,95; 38,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,02; 38,13</t>
+          <t>35,2; 38,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,95; 39,93</t>
+          <t>37,81; 39,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,87; 38,94</t>
+          <t>36,76; 38,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,92; 38,12</t>
+          <t>35,84; 37,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,31; 37,58</t>
+          <t>35,45; 37,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,55; 40,25</t>
+          <t>38,57; 40,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,54; 38,37</t>
+          <t>36,62; 38,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,93</t>
+          <t>36,14; 38,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,58; 38,16</t>
+          <t>36,55; 38,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,13; 39,72</t>
+          <t>38,24; 39,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,86; 38,83</t>
+          <t>36,9; 38,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,72</t>
+          <t>36,64; 38,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,5</t>
+          <t>36,97; 38,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,76</t>
+          <t>38,62; 39,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,35</t>
+          <t>37,02; 38,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,73; 38,01</t>
+          <t>36,69; 37,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,17</t>
+          <t>37,01; 38,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,0; 43,56</t>
+          <t>39,83; 43,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 40,88</t>
+          <t>35,68; 40,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,67; 39,55</t>
+          <t>35,65; 39,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,11; 41,92</t>
+          <t>37,27; 41,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 41,9</t>
+          <t>38,62; 41,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,66; 40,3</t>
+          <t>35,82; 40,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 40,61</t>
+          <t>35,46; 40,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,42; 38,66</t>
+          <t>34,52; 38,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,73; 42,12</t>
+          <t>39,77; 42,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,54; 40,03</t>
+          <t>36,54; 40,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,09; 39,47</t>
+          <t>36,25; 39,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,49; 39,6</t>
+          <t>36,47; 39,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 40,55</t>
+          <t>38,0; 40,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,45; 38,77</t>
+          <t>35,49; 38,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,44; 39,67</t>
+          <t>35,56; 39,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 38,41</t>
+          <t>36,09; 38,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,96; 39,73</t>
+          <t>36,86; 39,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 39,7</t>
+          <t>35,97; 39,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,21; 39,63</t>
+          <t>36,14; 39,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,54; 40,39</t>
+          <t>37,75; 40,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,84; 39,84</t>
+          <t>37,81; 39,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,25; 38,88</t>
+          <t>36,29; 38,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 38,99</t>
+          <t>36,3; 38,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 39,26</t>
+          <t>37,39; 39,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,4; 40,82</t>
+          <t>37,16; 40,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,83; 38,75</t>
+          <t>34,65; 38,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,73; 38,95</t>
+          <t>34,54; 39,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,15; 38,97</t>
+          <t>36,14; 39,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 39,74</t>
+          <t>36,62; 39,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,45; 39,61</t>
+          <t>35,35; 39,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,33; 39,29</t>
+          <t>35,28; 39,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,63; 39,14</t>
+          <t>35,58; 39,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,33; 39,75</t>
+          <t>37,07; 39,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,7; 38,59</t>
+          <t>35,63; 38,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,6; 38,58</t>
+          <t>35,62; 38,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,21; 38,48</t>
+          <t>36,34; 38,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 40,14</t>
+          <t>37,13; 40,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,22; 39,08</t>
+          <t>36,43; 39,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,97; 38,1</t>
+          <t>34,77; 38,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,52; 37,78</t>
+          <t>34,39; 37,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,83; 40,31</t>
+          <t>37,85; 40,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,4; 39,58</t>
+          <t>36,49; 39,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,95; 38,89</t>
+          <t>36,01; 38,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,2; 38,21</t>
+          <t>35,08; 38,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,81; 39,87</t>
+          <t>37,88; 39,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,88</t>
+          <t>36,84; 38,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,84; 37,95</t>
+          <t>35,83; 37,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 37,61</t>
+          <t>35,54; 37,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,57; 40,24</t>
+          <t>38,67; 40,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,62; 38,38</t>
+          <t>36,64; 38,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,14; 38,08</t>
+          <t>35,99; 37,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,55; 38,17</t>
+          <t>36,59; 38,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 39,72</t>
+          <t>38,17; 39,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,9; 38,84</t>
+          <t>36,94; 38,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,48</t>
+          <t>36,64; 38,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,97; 38,59</t>
+          <t>36,83; 38,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,71</t>
+          <t>38,64; 39,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,35</t>
+          <t>37,05; 38,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,69; 37,96</t>
+          <t>36,66; 37,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,08</t>
+          <t>37,0; 38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37,41</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41,69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>37,77</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,35</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,88</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,04</t>
+          <t>39,06</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,99</t>
+          <t>38,23</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,83; 43,39</t>
+          <t>38,67; 42,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 40,95</t>
+          <t>35,86; 40,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,65; 39,51</t>
+          <t>35,35; 40,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 41,75</t>
+          <t>35,25; 38,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,62; 41,88</t>
+          <t>40,05; 43,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,82; 40,65</t>
+          <t>35,7; 40,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,46; 40,6</t>
+          <t>35,42; 39,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,52; 38,58</t>
+          <t>37,28; 42,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,77; 42,23</t>
+          <t>39,81; 42,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,54; 40,18</t>
+          <t>36,49; 40,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,43</t>
+          <t>36,11; 39,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,47; 39,56</t>
+          <t>36,76; 39,81</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38,45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,92</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37,91</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38,75</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>39,29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>37,22</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>37,5</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,33</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,92</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,91</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,0</t>
+          <t>37,37</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,3</t>
+          <t>38,15</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,0; 40,7</t>
+          <t>36,97; 39,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,49; 38,8</t>
+          <t>35,89; 40,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,56; 39,41</t>
+          <t>36,14; 39,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 38,4</t>
+          <t>37,23; 40,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,86; 39,89</t>
+          <t>37,76; 40,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,97; 39,83</t>
+          <t>35,5; 38,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,5</t>
+          <t>35,32; 39,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,75; 40,62</t>
+          <t>36,09; 38,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,81; 39,76</t>
+          <t>37,87; 39,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,29; 38,72</t>
+          <t>36,3; 38,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 38,95</t>
+          <t>36,26; 38,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,39; 39,42</t>
+          <t>37,15; 39,06</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>38,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37,15</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>36,86</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>36,72</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,11</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,49</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,23</t>
+          <t>37,44</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,4</t>
+          <t>37,29</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,16; 40,54</t>
+          <t>36,44; 39,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,65; 38,77</t>
+          <t>35,08; 39,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,54; 39,07</t>
+          <t>35,16; 39,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,16</t>
+          <t>35,7; 38,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 39,85</t>
+          <t>37,17; 40,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,35; 39,31</t>
+          <t>34,68; 38,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,28; 39,25</t>
+          <t>34,56; 38,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,58; 39,05</t>
+          <t>35,89; 38,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,07; 39,61</t>
+          <t>37,36; 39,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,63; 38,58</t>
+          <t>35,71; 38,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,62; 38,53</t>
+          <t>35,54; 38,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,34; 38,64</t>
+          <t>36,06; 38,31</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,07</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37,0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>38,76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>36,45</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,07</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,48</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,85</t>
+          <t>36,46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,57</t>
+          <t>36,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,13; 40,34</t>
+          <t>37,67; 40,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,43; 39,08</t>
+          <t>36,16; 39,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 38,13</t>
+          <t>35,84; 38,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,39; 37,86</t>
+          <t>35,15; 38,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,85; 40,47</t>
+          <t>37,05; 40,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,49; 39,64</t>
+          <t>36,4; 39,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,01; 38,86</t>
+          <t>34,82; 38,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,08; 38,11</t>
+          <t>34,63; 38,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,88; 39,86</t>
+          <t>37,95; 39,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,84; 38,8</t>
+          <t>36,87; 38,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,83; 37,99</t>
+          <t>35,92; 38,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,54; 37,69</t>
+          <t>35,53; 37,76</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37,72</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>39,46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>37,51</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>37,03</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>37,42</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,57</t>
+          <t>37,58</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,31</t>
+          <t>38,13; 39,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,43</t>
+          <t>36,86; 38,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 37,95</t>
+          <t>36,76; 38,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,59; 38,2</t>
+          <t>36,86; 38,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,17; 39,66</t>
+          <t>38,55; 40,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,92</t>
+          <t>36,54; 38,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,54</t>
+          <t>36,0; 37,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,83; 38,5</t>
+          <t>36,67; 38,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,72</t>
+          <t>38,59; 39,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,66; 37,99</t>
+          <t>36,73; 38,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,0; 38,19</t>
+          <t>37,03; 38,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
+          <t>Número medio de horas a la semana que la persona entrevistada trabaja habitualmente (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40,35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,69</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,77</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39,06</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38,28</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37,83</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,23</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>40.34581945543115</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>38.09769023279446</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>37.87677663431975</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>37.40633808618151</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>41.68897062194394</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>38.47029285037433</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>37.76652993801181</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>39.06277629151744</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>40.99508979657949</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>38.27817024291663</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>37.82660938604644</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>38.22765404831457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>38,67; 42,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35,86; 40,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35,35; 40,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35,25; 38,81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>40,05; 43,75</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,7; 40,97</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,42; 39,68</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37,28; 42,45</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39,81; 42,27</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36,49; 40,03</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36,11; 39,42</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,76; 39,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>38.66863646374261</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>35.86291897599781</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>35.34519187681222</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>35.24556619705054</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>40.05316333069717</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>35.69916026770144</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>35.41878302093212</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>37.28271372593854</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>39.8141023535521</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>36.49065481510005</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>36.10737653978182</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>36.76334389348017</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>42.0603392120444</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>40.3741145379731</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>40.23048370557422</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>38.81413918034801</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>43.74527227045838</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>40.97031660207376</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>39.6801910929065</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>42.44924344878946</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>42.26954978315459</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>40.0297969695599</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>39.42070316273547</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>39.80633935092452</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>38,45</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37,92</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,75</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,29</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,22</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,5</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37,37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38,87</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37,59</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37,71</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>38,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>36,97; 39,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35,89; 40,09</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36,14; 39,6</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37,23; 40,19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37,76; 40,61</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,5; 38,62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,32; 39,5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36,09; 38,42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37,87; 39,81</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36,3; 38,85</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36,26; 38,85</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,15; 39,06</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>38.45044457297801</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>37.92137843082126</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>37.9086930104519</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>38.75207688572015</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>39.29246028834101</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>37.21923807614541</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>37.49972151867231</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>37.37456614721471</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>38.86627085836498</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>37.58813144276402</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>37.70830528823052</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>38.14883393641986</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>38,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,92</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,86</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,72</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37,44</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38,5</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>37,18</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37,09</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>37,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>36.97013509200796</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>35.89087786056361</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>36.13566205214865</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>37.2287018502149</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>37.76041449355851</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>35.50348935582048</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>35.32416642824916</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>36.08694763166891</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>37.86925588769044</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>36.30369724541759</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>36.26455639165047</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>37.14996492567349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>36,44; 39,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>35,08; 39,44</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35,16; 39,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>35,7; 38,89</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>37,17; 40,67</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>34,68; 38,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>34,56; 38,83</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35,89; 38,92</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37,36; 39,59</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35,71; 38,59</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35,54; 38,51</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,06; 38,31</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>39.88352326907557</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>40.08650769425295</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>39.60300868169621</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>40.18848888351476</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>40.6100454335422</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>38.6226733301364</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>39.50336475030066</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>38.42339603599136</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>39.81398188500988</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>38.84933080916111</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>38.85408619702048</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>39.06261426306103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>39,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38,07</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,76</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,45</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36,46</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37,89</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36,99</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,73</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>38.10659407764393</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>37.4912069370024</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>37.42661329363916</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>37.15165574698556</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>38.92401637422177</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>36.85638043922398</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36.71609447401704</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>37.44127078436873</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>38.49504278979144</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>37.17784468687396</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>37.08783447782995</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>37.28723263094683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>37,67; 40,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36,16; 39,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35,84; 38,84</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35,15; 38,3</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>37,05; 40,25</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,4; 39,09</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,82; 38,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34,63; 38,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37,95; 39,93</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36,87; 38,94</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35,92; 38,12</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,53; 37,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>36.44139536989727</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>35.08363507863379</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>35.16165075460686</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>35.70465799750164</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>37.16680919929739</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>34.67781613596262</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>34.5641584861314</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>35.88721776721813</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>37.36058287671764</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>35.70562336734693</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>35.54159363878706</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>36.05777227954831</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>39.75609949052695</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>39.43785454206737</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>39.53646043881897</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>38.89472529775626</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>40.66907502483561</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>38.72072170011074</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>38.83131558620089</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>38.91679096568856</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>39.58835554363318</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>38.58678428318301</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>38.51459189238235</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>38.30997537818939</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>39.15014523723161</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>38.06612692840124</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>37.47503056056533</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>37.00152544644781</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>38.75824998130973</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>37.70182386355983</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>36.45188558007684</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>36.46166934917893</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>38.95912775080999</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>37.88554774757829</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>36.98858688076053</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>36.7308554276807</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>37.67312745634015</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>36.16088149405989</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>35.84035859869199</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>35.14770448038137</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>37.0493865414881</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>36.40424176718404</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>34.8217647780757</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>34.63291993640009</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>37.95411562627943</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>36.87271949077692</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>35.91665692903609</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>35.53021085356202</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>40.41695793883041</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>39.57387488309188</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>38.83993116152952</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>38.30078804215729</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>40.25261466784891</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>39.09463068641437</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>38.16452625464771</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>38.00239642949666</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>39.92685523804115</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>38.93869032943217</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>38.11681813257903</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>37.75927714213941</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>39,46</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,51</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,03</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37,42</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39,2</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37,71</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37,36</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>38,13; 39,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,83</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36,76; 38,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38,55; 40,25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,54; 38,37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,0; 37,93</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36,67; 38,22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38,59; 39,76</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37,05; 38,35</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>36,73; 38,01</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,03; 38,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>38.9617474409111</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>37.90219074550711</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>37.65356141937377</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>37.71831790625583</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>39.45980613506651</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>37.51110710414096</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>37.02884430379743</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>37.42407225162071</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>39.20382566576855</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>37.71164114895484</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>37.35608325700891</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>37.57967040272774</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>38.12523773764376</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>36.86293348712334</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>36.75545481731248</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>36.86144092227822</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>38.5533698392418</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>36.54003255877122</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>35.99740135009402</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>36.66954540489485</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>38.58758848846494</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>37.04987776274685</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>36.73002015215267</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>37.02791775350198</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>39.72393772825984</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>38.82678992143239</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>38.72199535822551</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>38.45406183983179</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>40.24687479746343</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>38.37038867402762</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>37.92503434363419</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>38.21766268070953</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>39.75863437497605</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>38.35263565720574</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>38.01489188576743</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>38.17214592169135</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
